--- a/specs/Wiring_5/Wiring_5_spec.xlsx
+++ b/specs/Wiring_5/Wiring_5_spec.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Разъёмы'!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Распиновка'!$A$1:$N$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BOM'!$A$1:$J$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Замечания'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Замечания'!$A$1:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Каталог'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3503,7 +3503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3658,8 +3658,28 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Контакты не указаны в BOM</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Для части разъёмов (Yazaki, VAG, Molex NSCC, колодки ВАЗ) контакты в BOM не указаны или указаны без номера.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Подобрать по каталогу производителя корпуса под 0.5–1.0 мм².</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D8"/>
+  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
